--- a/scripts/productos-digitales/guia-churreria/build/calculadora-capex-churreria.xlsx
+++ b/scripts/productos-digitales/guia-churreria/build/calculadora-capex-churreria.xlsx
@@ -4306,7 +4306,7 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>Supuesto declarado. Nunca la horquilla de licencias de nuestro post.</t>
+          <t>Supuesto declarado.</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="J11" s="22">
         <f>IFERROR(J30/I30,"")</f>
-        <v>0.13047271012613462</v>
+        <v>0.13047271012613465</v>
       </c>
       <c r="K11" s="26">
         <f>IF(E11="No","",H11)</f>
@@ -4571,11 +4571,11 @@
       </c>
       <c r="L11" s="26">
         <f>IF(K11="","",J30)</f>
-        <v>110.67999999999999</v>
+        <v>110.68</v>
       </c>
       <c r="M11" s="26">
         <f>IF(K11="","",K11+L11)</f>
-        <v>958.9799999999999</v>
+        <v>958.98</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="J30" s="11">
         <f>SUM(J16:J29)</f>
-        <v>110.67999999999999</v>
+        <v>110.68</v>
       </c>
       <c r="K30" s="11">
         <f>SUM(K16:K29)</f>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>supuesto (nunca la horquilla de nuestro post)</t>
+          <t>supuesto declarado</t>
         </is>
       </c>
     </row>
@@ -5962,11 +5962,11 @@
       </c>
       <c r="F43" s="26">
         <f>SUMIF('Equipamiento Línea a Línea'!$B$6:$B$33,B43,'Equipamiento Línea a Línea'!$P$6:$P$33)+SUMIF($B$6:$B$12,B43,$L$6:$L$12)</f>
-        <v>110.67999999999999</v>
+        <v>110.68</v>
       </c>
       <c r="G43" s="26">
         <f>E43+F43</f>
-        <v>958.9799999999999</v>
+        <v>958.98</v>
       </c>
       <c r="H43" s="22">
         <f>IFERROR(E43/$E$45,"")</f>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>Viaja al libro 6 desde «Resumen» (L5). El libro 6 le suma el fondo de maniobra de los primeros meses: aquí no está.</t>
+          <t>Viaja al libro 6 desde «Resumen». El libro 6 le suma el fondo de maniobra de los primeros meses: aquí no está.</t>
         </is>
       </c>
     </row>
@@ -10692,8 +10692,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="2">
+    <mergeCell ref="A27:K27"/>
     <mergeCell ref="A26:K26"/>
-    <mergeCell ref="A27:K27"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Sí o No" error="Elige una opción de la lista." type="list">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Sembrado con el traspaso con sala de Vallecas: 74 m², precio PEDIDO y negociable, con los equipos dentro. Es el techo de los anuncios leídos para un local con sala. Lectura del 3-oct no reabierta por el captcha: se comprueba antes de publicar la guía.</t>
+          <t>Sembrado con el traspaso con sala de Vallecas: 74 m², precio PEDIDO y negociable, con los equipos dentro. Es el techo de los anuncios leídos para un local con sala. Lectura del anuncio del 3-10-2026, sin reverificar: compruébalo en el anuncio antes de usarlo.</t>
         </is>
       </c>
     </row>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Precio pedido y negociable, con unos 50.000 € de equipos declarados dentro y la misma renta que El Molinete. Lectura del 3-oct no reabierta por el captcha: se comprueba antes de publicar la guía.</t>
+          <t>Precio pedido y negociable, con unos 50.000 € de equipos declarados dentro y la misma renta que El Molinete. Lectura del anuncio del 3-10-2026, sin reverificar: compruébalo en el anuncio antes de usarlo.</t>
         </is>
       </c>
       <c r="F35" s="26">
@@ -11782,11 +11782,11 @@
       </c>
       <c r="C15" s="26">
         <f>'CAPEX por Bloque'!$F$43</f>
-        <v>110.67999999999999</v>
+        <v>110.68</v>
       </c>
       <c r="D15" s="26">
         <f>'CAPEX por Bloque'!$G$43</f>
-        <v>958.9799999999999</v>
+        <v>958.98</v>
       </c>
     </row>
     <row r="16">
